--- a/CapPlaywright/testdata/readexcel.xlsx
+++ b/CapPlaywright/testdata/readexcel.xlsx
@@ -1,27 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sheet2" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Sheet3" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Sheet4" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Sheet5" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Sheet6" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>hiiiii</t>
   </si>
@@ -29,27 +27,27 @@
     <t>a1</t>
   </si>
   <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>a3</t>
+  </si>
+  <si>
     <t>b1</t>
   </si>
   <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>b3</t>
+  </si>
+  <si>
     <t>c1</t>
   </si>
   <si>
-    <t>a2</t>
-  </si>
-  <si>
-    <t>b2</t>
-  </si>
-  <si>
     <t>c2</t>
   </si>
   <si>
-    <t>a3</t>
-  </si>
-  <si>
-    <t>b3</t>
-  </si>
-  <si>
     <t>c4</t>
   </si>
   <si>
@@ -81,6 +79,54 @@
   </si>
   <si>
     <t>radhika@23</t>
+  </si>
+  <si>
+    <t>playwright</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>sona@gmail.com</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>Riya</t>
+  </si>
+  <si>
+    <t>riya@gmail.com</t>
+  </si>
+  <si>
+    <t>56789</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>aman@gmail.com</t>
+  </si>
+  <si>
+    <t>98765</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>rahul@gmail.com</t>
+  </si>
+  <si>
+    <t>45678</t>
+  </si>
+  <si>
+    <t>Bacca Bucci</t>
   </si>
 </sst>
 </file>
@@ -89,19 +135,19 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,16 +167,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -409,10 +453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -425,36 +469,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -468,14 +512,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -486,7 +530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -497,7 +541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -518,4 +562,142 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>